--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50523,10 +50523,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1388万
+$35,668/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$2009万
+$35,122/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 850呎 (3房)
+$3362万
+$39,552/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2095呎 (4+房)
 $11000万
@@ -50534,7 +50571,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1294呎 (4+房)
 $5406万
@@ -50542,7 +50579,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1294呎 (4+房)
 $5500万
@@ -50550,9 +50587,9 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1866呎 (4+房)
 $9580万
@@ -50560,44 +50597,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1388万
-$35,668/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$2009万
-$35,122/呎
-(21年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 850呎 (3房)
-$3362万
-$39,552/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50655,10 +50655,40 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39&amp;40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4163万
+$32,222/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5422万
@@ -50666,9 +50696,9 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1340万
@@ -50676,7 +50706,7 @@
 (21年-05月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1993万
@@ -50684,7 +50714,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $6600万
@@ -50692,7 +50722,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3289万
@@ -50700,36 +50730,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39&amp;40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4163万
-$32,222/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51183,10 +51183,40 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4880万
@@ -51194,9 +51224,9 @@
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,7 +51234,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1773万
@@ -51212,7 +51242,7 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>25304000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>27005</v>
+        <v>26977</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>25304000</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>27005</v>
+        <v>26977</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2095呎 (4+房)
+$11000万
+$52,506/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1294呎 (4+房)
+$5406万
+$41,780/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1294呎 (4+房)
+$5500万
+$42,504/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1866呎 (4+房)
+$9580万
+$51,340/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>
@@ -52797,9 +52797,9 @@
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>F | 937呎 (3房)
+          <t>F | 938呎 (3房)
 $2530万
-$27,005/呎
+$26,977/呎
 (21年-05月-25日)</t>
         </is>
       </c>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50655,11 +50655,62 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5422万
+$44,963/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1340万
+$34,455/呎
+(21年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1993万
+$34,841/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$6600万
+$54,187/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3289万
+$39,160/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39&amp;40</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4163万
@@ -50667,7 +50718,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4278万
@@ -50675,61 +50726,10 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5422万
-$44,963/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1340万
-$34,455/呎
-(21年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1993万
-$34,841/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$6600万
-$54,187/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3289万
-$39,160/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1848万
+$32,260/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50787,11 +50787,62 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5434万
+$45,054/呎
+(21年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1321万
+$34,480/呎
+(21年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1822万
+$31,803/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5288万
+$43,415/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3102万
+$36,926/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4222万
@@ -50799,7 +50850,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4220万
@@ -50807,61 +50858,10 @@
 (25年-03月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5434万
-$45,054/呎
-(21年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1321万
-$34,480/呎
-(21年-05月-01日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1822万
-$31,803/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5288万
-$43,415/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3102万
-$36,926/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$3988万
+$33,068/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50523,10 +50523,47 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1388万
+$35,668/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$2009万
+$35,122/呎
+(21年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 850呎 (3房)
+$3362万
+$39,552/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41&amp;42</t>
         </is>
       </c>
-      <c r="B6" s="21" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>A | 2095呎 (4+房)
 $11000万
@@ -50534,7 +50571,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 1294呎 (4+房)
 $5406万
@@ -50542,7 +50579,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t>C | 1294呎 (4+房)
 $5500万
@@ -50550,9 +50587,9 @@
 (26年-07月-06日)</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
-      <c r="F6" s="20" t="inlineStr"/>
-      <c r="G6" s="21" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>F | 1866呎 (4+房)
 $9580万
@@ -50560,44 +50597,7 @@
 (24年-03月-27日)</t>
         </is>
       </c>
-      <c r="H6" s="20" t="inlineStr"/>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1388万
-$35,668/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$2009万
-$35,122/呎
-(21年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>G | 850呎 (3房)
-$3362万
-$39,552/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50655,10 +50655,40 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39&amp;40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4163万
+$32,222/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5422万
@@ -50666,9 +50696,9 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1340万
@@ -50676,7 +50706,7 @@
 (21年-05月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1993万
@@ -50684,7 +50714,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $6600万
@@ -50692,7 +50722,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3289万
@@ -50700,36 +50730,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39&amp;40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4163万
-$32,222/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50787,10 +50787,40 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5434万
@@ -50798,9 +50828,9 @@
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,7 +50838,7 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1822万
@@ -50816,7 +50846,7 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51315,10 +51315,40 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5018万
@@ -51326,9 +51356,9 @@
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,7 +51366,7 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1595万
@@ -51344,7 +51374,7 @@
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50655,11 +50655,62 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5422万
+$44,963/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1340万
+$34,455/呎
+(21年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1993万
+$34,841/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$6600万
+$54,187/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3289万
+$39,160/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39&amp;40</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4163万
@@ -50667,7 +50718,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4278万
@@ -50675,61 +50726,10 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5422万
-$44,963/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1340万
-$34,455/呎
-(21年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1993万
-$34,841/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$6600万
-$54,187/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3289万
-$39,160/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50655,10 +50655,40 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39&amp;40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4163万
+$32,222/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5422万
@@ -50666,9 +50696,9 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1340万
@@ -50676,7 +50706,7 @@
 (21年-05月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1993万
@@ -50684,7 +50714,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $6600万
@@ -50692,7 +50722,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3289万
@@ -50700,36 +50730,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39&amp;40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4163万
-$32,222/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50787,11 +50787,62 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5434万
+$45,054/呎
+(21年-06月-17日)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1321万
+$34,480/呎
+(21年-05月-01日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1822万
+$31,803/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5288万
+$43,415/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3102万
+$36,926/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37&amp;38</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr"/>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4222万
@@ -50799,7 +50850,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4220万
@@ -50807,61 +50858,10 @@
 (25年-03月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
-      <c r="F12" s="20" t="inlineStr"/>
-      <c r="G12" s="20" t="inlineStr"/>
-      <c r="H12" s="20" t="inlineStr"/>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5434万
-$45,054/呎
-(21年-06月-17日)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr"/>
-      <c r="D13" s="20" t="inlineStr"/>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1321万
-$34,480/呎
-(21年-05月-01日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1822万
-$31,803/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5288万
-$43,415/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3102万
-$36,926/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E13" s="20" t="inlineStr"/>
+      <c r="F13" s="20" t="inlineStr"/>
+      <c r="G13" s="20" t="inlineStr"/>
+      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,10 +51579,40 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23&amp;25</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4365万
+$33,786/呎
+(24年-05月-03日)</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3948万
+$30,556/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr"/>
+      <c r="G30" s="20" t="inlineStr"/>
+      <c r="H30" s="20" t="inlineStr"/>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $3988万
@@ -51590,9 +51620,9 @@
 (24年-02月-01日)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr"/>
-      <c r="D30" s="20" t="inlineStr"/>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr"/>
+      <c r="D31" s="20" t="inlineStr"/>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1236万
@@ -51600,7 +51630,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="F30" s="21" t="inlineStr">
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1726万
@@ -51608,7 +51638,7 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3600万
@@ -51616,7 +51646,7 @@
 (24年-11月-07日)</t>
         </is>
       </c>
-      <c r="H30" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2783万
@@ -51624,36 +51654,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23&amp;25</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr"/>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4365万
-$33,786/呎
-(24年-05月-03日)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3948万
-$30,556/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="inlineStr"/>
-      <c r="F31" s="20" t="inlineStr"/>
-      <c r="G31" s="20" t="inlineStr"/>
-      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,10 +51447,40 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4840万
@@ -51458,9 +51488,9 @@
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,7 +51498,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1789万
@@ -51476,7 +51506,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50655,11 +50655,62 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5422万
+$44,963/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (1房)
+$1340万
+$34,455/呎
+(21年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1993万
+$34,841/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$6600万
+$54,187/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3289万
+$39,160/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39&amp;40</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4163万
@@ -50667,7 +50718,7 @@
 (26年-01月-12日)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4278万
@@ -50675,61 +50726,10 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
-      <c r="F9" s="20" t="inlineStr"/>
-      <c r="G9" s="20" t="inlineStr"/>
-      <c r="H9" s="20" t="inlineStr"/>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5422万
-$44,963/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr"/>
-      <c r="E10" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (1房)
-$1340万
-$34,455/呎
-(21年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1993万
-$34,841/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$6600万
-$54,187/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3289万
-$39,160/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
+      <c r="E10" s="20" t="inlineStr"/>
+      <c r="F10" s="20" t="inlineStr"/>
+      <c r="G10" s="20" t="inlineStr"/>
+      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -51315,11 +51315,62 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$5018万
+$41,609/呎
+(21年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr"/>
+      <c r="D24" s="20" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1298万
+$33,883/呎
+(21年-05月-24日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1595万
+$27,834/呎
+(24年-03月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5000万
+$41,051/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2957万
+$35,204/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28&amp;29</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr"/>
-      <c r="C24" s="21" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4091万
@@ -51327,7 +51378,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4039万
@@ -51335,61 +51386,10 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="E24" s="20" t="inlineStr"/>
-      <c r="F24" s="20" t="inlineStr"/>
-      <c r="G24" s="20" t="inlineStr"/>
-      <c r="H24" s="20" t="inlineStr"/>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$5018万
-$41,609/呎
-(21年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr"/>
-      <c r="D25" s="20" t="inlineStr"/>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1298万
-$33,883/呎
-(21年-05月-24日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1595万
-$27,834/呎
-(24年-03月-21日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5000万
-$41,051/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2957万
-$35,204/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E25" s="20" t="inlineStr"/>
+      <c r="F25" s="20" t="inlineStr"/>
+      <c r="G25" s="20" t="inlineStr"/>
+      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50655,10 +50655,40 @@
     <row r="9" ht="58" customHeight="1">
       <c r="A9" s="19" t="inlineStr">
         <is>
+          <t>39&amp;40</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4163万
+$32,222/呎
+(26年-01月-12日)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
+      <c r="G9" s="20" t="inlineStr"/>
+      <c r="H9" s="20" t="inlineStr"/>
+      <c r="I9" s="20" t="inlineStr"/>
+      <c r="J9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $5422万
@@ -50666,9 +50696,9 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="21" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr"/>
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1340万
@@ -50676,7 +50706,7 @@
 (21年-05月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $1993万
@@ -50684,7 +50714,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G10" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $6600万
@@ -50692,7 +50722,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3289万
@@ -50700,36 +50730,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I9" s="20" t="inlineStr"/>
-      <c r="J9" s="20" t="inlineStr"/>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>39&amp;40</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr"/>
-      <c r="C10" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4163万
-$32,222/呎
-(26年-01月-12日)</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
-      <c r="F10" s="20" t="inlineStr"/>
-      <c r="G10" s="20" t="inlineStr"/>
-      <c r="H10" s="20" t="inlineStr"/>
       <c r="I10" s="20" t="inlineStr"/>
       <c r="J10" s="20" t="inlineStr"/>
     </row>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1878万
+$32,770/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51051,10 +51051,40 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32&amp;33</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4190万
+$32,430/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4133万
+$31,987/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
+      <c r="F18" s="20" t="inlineStr"/>
+      <c r="G18" s="20" t="inlineStr"/>
+      <c r="H18" s="20" t="inlineStr"/>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5000万
@@ -51062,9 +51092,9 @@
 (23年-03月-10日)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr"/>
-      <c r="D18" s="20" t="inlineStr"/>
-      <c r="E18" s="21" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr"/>
+      <c r="D19" s="20" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1292万
@@ -51072,7 +51102,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F18" s="21" t="inlineStr">
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1848万
@@ -51080,7 +51110,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $4820万
@@ -51088,7 +51118,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3152万
@@ -51096,36 +51126,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32&amp;33</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr"/>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4190万
-$32,430/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4133万
-$31,987/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr"/>
-      <c r="F19" s="20" t="inlineStr"/>
-      <c r="G19" s="20" t="inlineStr"/>
-      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51183,10 +51183,40 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>A | 1206呎 (4+房)
 $4880万
@@ -51194,9 +51224,9 @@
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,7 +51234,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1773万
@@ -51212,7 +51242,7 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51447,11 +51447,62 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4840万
+$40,137/呎
+(21年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr"/>
+      <c r="D27" s="20" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1288万
+$33,632/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1789万
+$31,220/呎
+(21年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3664万
+$30,079/呎
+(24年-10月-18日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2810万
+$33,457/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26&amp;27</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr"/>
-      <c r="C27" s="21" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4630万
@@ -51459,7 +51510,7 @@
 (23年-06月-21日)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3998万
@@ -51467,61 +51518,10 @@
 (24年-11月-14日)</t>
         </is>
       </c>
-      <c r="E27" s="20" t="inlineStr"/>
-      <c r="F27" s="20" t="inlineStr"/>
-      <c r="G27" s="20" t="inlineStr"/>
-      <c r="H27" s="20" t="inlineStr"/>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4840万
-$40,137/呎
-(21年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr"/>
-      <c r="D28" s="20" t="inlineStr"/>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1288万
-$33,632/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1789万
-$31,220/呎
-(21年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3664万
-$30,079/呎
-(24年-10月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2810万
-$33,457/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E28" s="20" t="inlineStr"/>
+      <c r="F28" s="20" t="inlineStr"/>
+      <c r="G28" s="20" t="inlineStr"/>
+      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -50919,10 +50919,40 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35&amp;36</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4570万
+$35,372/呎
+(26年-05月-05日)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4335万
+$33,556/呎
+(25年-03月-12日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr"/>
+      <c r="F15" s="20" t="inlineStr"/>
+      <c r="G15" s="20" t="inlineStr"/>
+      <c r="H15" s="20" t="inlineStr"/>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="B15" s="21" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>A | 1205呎 (4+房)
 $5246万
@@ -50930,9 +50960,9 @@
 (21年-06月-03日)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr"/>
-      <c r="D15" s="20" t="inlineStr"/>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr"/>
+      <c r="D16" s="20" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1314万
@@ -50940,7 +50970,7 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 573呎 (2房)
 $1878万
@@ -50948,7 +50978,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5176万
@@ -50956,7 +50986,7 @@
 (21年-06月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3071万
@@ -50964,36 +50994,6 @@
 (21年-05月-14日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35&amp;36</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4570万
-$35,372/呎
-(26年-05月-05日)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4335万
-$33,556/呎
-(25年-03月-12日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-      <c r="F16" s="20" t="inlineStr"/>
-      <c r="G16" s="20" t="inlineStr"/>
-      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51183,11 +51183,62 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 1206呎 (4+房)
+$4880万
+$40,466/呎
+(21年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr"/>
+      <c r="D21" s="20" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1255万
+$32,770/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 573呎 (2房)
+$1773万
+$30,935/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3992万
+$32,778/呎
+(24年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2867万
+$34,131/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30&amp;31</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="21" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4278万
@@ -51195,7 +51246,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4076万
@@ -51203,61 +51254,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E21" s="20" t="inlineStr"/>
-      <c r="F21" s="20" t="inlineStr"/>
-      <c r="G21" s="20" t="inlineStr"/>
-      <c r="H21" s="20" t="inlineStr"/>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$4880万
-$40,466/呎
-(21年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="C22" s="20" t="inlineStr"/>
-      <c r="D22" s="20" t="inlineStr"/>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1255万
-$32,770/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1773万
-$30,935/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3992万
-$32,778/呎
-(24年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2867万
-$34,131/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
+      <c r="E22" s="20" t="inlineStr"/>
+      <c r="F22" s="20" t="inlineStr"/>
+      <c r="G22" s="20" t="inlineStr"/>
+      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>

--- a/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-晋环/晋环_销控明细表.xlsx
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>95800000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>51340</v>
+        <v>51312</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>95800000</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>51340</v>
+        <v>51312</v>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1294</v>
+        <v>1285</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>55000000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>42504</v>
+        <v>42802</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>55000000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>42504</v>
+        <v>42802</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1294</v>
+        <v>1284</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>54063000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>41780</v>
+        <v>42105</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1157,7 +1157,7 @@
         <v>54063000</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>41780</v>
+        <v>42105</v>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2095</v>
+        <v>2084</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
         <v>110000000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>52506</v>
+        <v>52783</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>110000000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>52506</v>
+        <v>52783</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>56635000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>46961</v>
+        <v>47000</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>56635000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>46961</v>
+        <v>47000</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>54225000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>44963</v>
+        <v>45000</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>54225000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>44963</v>
+        <v>45000</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>53020000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>43964</v>
+        <v>44000</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>53020000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>43964</v>
+        <v>44000</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>18223000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>31803</v>
+        <v>31858</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
         <v>18223000</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>31803</v>
+        <v>31858</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>54335000</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>45054</v>
+        <v>45091</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>54335000</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>45054</v>
+        <v>45091</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>18168000</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>31707</v>
+        <v>31762</v>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>18168000</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>31707</v>
+        <v>31762</v>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
@@ -3176,7 +3176,7 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>18777000</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>32770</v>
+        <v>32827</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>18777000</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>32770</v>
+        <v>32827</v>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
         <v>18485000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>32260</v>
+        <v>32316</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3947,7 +3947,7 @@
         <v>18485000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>32260</v>
+        <v>32316</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>16045000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>28002</v>
+        <v>28051</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>16045000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>28002</v>
+        <v>28051</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         <v>17726000</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>30935</v>
+        <v>30990</v>
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>17726000</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>30935</v>
+        <v>30990</v>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4928,7 +4928,7 @@
         <v>48802500</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>40466</v>
+        <v>40500</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>48802500</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>40466</v>
+        <v>40500</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>15949000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>27834</v>
+        <v>27883</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5125,7 +5125,7 @@
         <v>15949000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>27834</v>
+        <v>27883</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5238,7 +5238,7 @@
         <v>52779000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>43764</v>
+        <v>43800</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         <v>52779000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>43764</v>
+        <v>43800</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5424,7 +5424,7 @@
         <v>15949000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>27834</v>
+        <v>27883</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>15949000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>27834</v>
+        <v>27883</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>50180000</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>41609</v>
+        <v>41643</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>50180000</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>41609</v>
+        <v>41643</v>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5858,7 +5858,7 @@
         <v>15854000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>27668</v>
+        <v>27717</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>15854000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>27668</v>
+        <v>27717</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="E90" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
@@ -6168,7 +6168,7 @@
         <v>17889000</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>31220</v>
+        <v>31274</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>17889000</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>31220</v>
+        <v>31274</v>
       </c>
       <c r="M90" s="3" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6416,7 +6416,7 @@
         <v>48404850</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>40137</v>
+        <v>40170</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6427,7 +6427,7 @@
         <v>48404850</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>40137</v>
+        <v>40170</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7160,7 +7160,7 @@
         <v>39880000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>33068</v>
+        <v>33095</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>39880000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>33068</v>
+        <v>33095</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         </is>
       </c>
       <c r="E109" s="4" t="n">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>17833000</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>31122</v>
+        <v>31177</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -7357,7 +7357,7 @@
         <v>17833000</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>31122</v>
+        <v>31177</v>
       </c>
       <c r="M109" s="3" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="E114" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>12629000</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>32718</v>
+        <v>32633</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         <v>12629000</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>32718</v>
+        <v>32633</v>
       </c>
       <c r="M114" s="3" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -7842,7 +7842,7 @@
         <v>27269000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>29071</v>
+        <v>29102</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -7853,7 +7853,7 @@
         <v>27269000</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>29071</v>
+        <v>29102</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="E122" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>42335500</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>37267</v>
+        <v>37300</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>42335500</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>37267</v>
+        <v>37300</v>
       </c>
       <c r="M122" s="3" t="inlineStr">
         <is>
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="E123" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F123" s="3" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         <v>12147000</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>31469</v>
+        <v>31388</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>12147000</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>31469</v>
+        <v>31388</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="E126" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
@@ -8400,7 +8400,7 @@
         <v>26228000</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>27962</v>
+        <v>27991</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>26228000</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>27962</v>
+        <v>27991</v>
       </c>
       <c r="M126" s="3" t="inlineStr">
         <is>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="E132" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
@@ -8772,7 +8772,7 @@
         <v>12553000</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>32521</v>
+        <v>32437</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>12553000</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>32521</v>
+        <v>32437</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>26150000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>27878</v>
+        <v>27908</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>26150000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>27878</v>
+        <v>27908</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         <v>41427500</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>36468</v>
+        <v>36500</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>41427500</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>36468</v>
+        <v>36500</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>12479000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>32329</v>
+        <v>32245</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
         <v>12479000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>32329</v>
+        <v>32245</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         </is>
       </c>
       <c r="E144" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>26236000</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>27970</v>
+        <v>28000</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>26236000</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>27970</v>
+        <v>28000</v>
       </c>
       <c r="M144" s="3" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>26864000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>28640</v>
+        <v>28670</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>26864000</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>28640</v>
+        <v>28670</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>41050000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>36136</v>
+        <v>36167</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>41050000</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>36136</v>
+        <v>36167</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         </is>
       </c>
       <c r="E168" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>12405000</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>32137</v>
+        <v>32054</v>
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>12405000</v>
       </c>
       <c r="L168" s="5" t="n">
-        <v>32137</v>
+        <v>32054</v>
       </c>
       <c r="M168" s="3" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         </is>
       </c>
       <c r="E176" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F176" s="3" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>39482000</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>34755</v>
+        <v>34786</v>
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
@@ -11511,7 +11511,7 @@
         <v>39482000</v>
       </c>
       <c r="L176" s="5" t="n">
-        <v>34755</v>
+        <v>34786</v>
       </c>
       <c r="M176" s="3" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         </is>
       </c>
       <c r="E177" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F177" s="3" t="inlineStr">
         <is>
@@ -11562,7 +11562,7 @@
         <v>12367000</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>32039</v>
+        <v>31956</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>12367000</v>
       </c>
       <c r="L177" s="5" t="n">
-        <v>32039</v>
+        <v>31956</v>
       </c>
       <c r="M177" s="3" t="inlineStr">
         <is>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="E180" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F180" s="3" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>26704000</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>28469</v>
+        <v>28499</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>26704000</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>28469</v>
+        <v>28499</v>
       </c>
       <c r="M180" s="3" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="E185" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F185" s="3" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
         <v>40804000</v>
       </c>
       <c r="I185" s="5" t="n">
-        <v>35919</v>
+        <v>35951</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -12069,7 +12069,7 @@
         <v>40804000</v>
       </c>
       <c r="L185" s="5" t="n">
-        <v>35919</v>
+        <v>35951</v>
       </c>
       <c r="M185" s="3" t="inlineStr">
         <is>
@@ -12104,7 +12104,7 @@
         </is>
       </c>
       <c r="E186" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F186" s="3" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>11895000</v>
       </c>
       <c r="I186" s="5" t="n">
-        <v>30816</v>
+        <v>30736</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -12131,7 +12131,7 @@
         <v>11895000</v>
       </c>
       <c r="L186" s="5" t="n">
-        <v>30816</v>
+        <v>30736</v>
       </c>
       <c r="M186" s="3" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         </is>
       </c>
       <c r="E203" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F203" s="3" t="inlineStr">
         <is>
@@ -13174,7 +13174,7 @@
         <v>40561000</v>
       </c>
       <c r="I203" s="5" t="n">
-        <v>35705</v>
+        <v>35737</v>
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>40561000</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>35705</v>
+        <v>35737</v>
       </c>
       <c r="M203" s="3" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         </is>
       </c>
       <c r="E222" s="4" t="n">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F222" s="3" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>9262000</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>23995</v>
+        <v>23933</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>9262000</v>
       </c>
       <c r="L222" s="5" t="n">
-        <v>23995</v>
+        <v>23933</v>
       </c>
       <c r="M222" s="3" t="inlineStr">
         <is>
@@ -14832,7 +14832,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>37982000</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>33435</v>
+        <v>33464</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -14859,7 +14859,7 @@
         <v>37982000</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>33435</v>
+        <v>33464</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15080,7 +15080,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>25304000</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>26977</v>
+        <v>27005</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>25304000</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>26977</v>
+        <v>27005</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         </is>
       </c>
       <c r="E239" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F239" s="3" t="inlineStr">
         <is>
@@ -15406,7 +15406,7 @@
         <v>38981000</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>34314</v>
+        <v>34344</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>38981000</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>34314</v>
+        <v>34344</v>
       </c>
       <c r="M239" s="3" t="inlineStr">
         <is>
@@ -15948,7 +15948,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>35525500</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>31272</v>
+        <v>31300</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>35525500</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>31272</v>
+        <v>31300</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>16601000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>34876</v>
+        <v>34949</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16099,7 +16099,7 @@
         <v>16601000</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>34876</v>
+        <v>34949</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         </is>
       </c>
       <c r="E254" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F254" s="3" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>16276000</v>
       </c>
       <c r="I254" s="5" t="n">
-        <v>34193</v>
+        <v>34265</v>
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
@@ -16347,7 +16347,7 @@
         <v>16276000</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>34193</v>
+        <v>34265</v>
       </c>
       <c r="M254" s="3" t="inlineStr">
         <is>
@@ -16568,7 +16568,7 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
@@ -16584,7 +16584,7 @@
         <v>16036000</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>33689</v>
+        <v>33760</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>16036000</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>33689</v>
+        <v>33760</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
@@ -17064,7 +17064,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>15009000</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>31532</v>
+        <v>31598</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>15009000</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>31532</v>
+        <v>31598</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         </is>
       </c>
       <c r="E274" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F274" s="3" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         <v>14920000</v>
       </c>
       <c r="I274" s="5" t="n">
-        <v>31345</v>
+        <v>31411</v>
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
@@ -17587,7 +17587,7 @@
         <v>14920000</v>
       </c>
       <c r="L274" s="5" t="n">
-        <v>31345</v>
+        <v>31411</v>
       </c>
       <c r="M274" s="3" t="inlineStr">
         <is>
@@ -17808,7 +17808,7 @@
         </is>
       </c>
       <c r="E278" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F278" s="3" t="inlineStr">
         <is>
@@ -17824,7 +17824,7 @@
         <v>15419000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>32393</v>
+        <v>32461</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17835,7 +17835,7 @@
         <v>15419000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>32393</v>
+        <v>32461</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         </is>
       </c>
       <c r="E286" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F286" s="3" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
         <v>14786000</v>
       </c>
       <c r="I286" s="5" t="n">
-        <v>31063</v>
+        <v>31128</v>
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>14786000</v>
       </c>
       <c r="L286" s="5" t="n">
-        <v>31063</v>
+        <v>31128</v>
       </c>
       <c r="M286" s="3" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         </is>
       </c>
       <c r="E294" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F294" s="3" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>12029000</v>
       </c>
       <c r="I294" s="5" t="n">
-        <v>25271</v>
+        <v>25324</v>
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
@@ -18827,7 +18827,7 @@
         <v>12029000</v>
       </c>
       <c r="L294" s="5" t="n">
-        <v>25271</v>
+        <v>25324</v>
       </c>
       <c r="M294" s="3" t="inlineStr">
         <is>
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -19560,7 +19560,7 @@
         <v>15099000</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>31721</v>
+        <v>31787</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>15099000</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>31721</v>
+        <v>31787</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="E310" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
@@ -19808,7 +19808,7 @@
         <v>15054000</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>31626</v>
+        <v>31693</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>15054000</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>31626</v>
+        <v>31693</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
@@ -20536,7 +20536,7 @@
         </is>
       </c>
       <c r="E322" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F322" s="3" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>14393000</v>
       </c>
       <c r="I322" s="5" t="n">
-        <v>30237</v>
+        <v>30301</v>
       </c>
       <c r="J322" s="3" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>14393000</v>
       </c>
       <c r="L322" s="5" t="n">
-        <v>30237</v>
+        <v>30301</v>
       </c>
       <c r="M322" s="3" t="inlineStr">
         <is>
@@ -20784,7 +20784,7 @@
         </is>
       </c>
       <c r="E326" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F326" s="3" t="inlineStr">
         <is>
@@ -20800,7 +20800,7 @@
         <v>14350000</v>
       </c>
       <c r="I326" s="5" t="n">
-        <v>30147</v>
+        <v>30211</v>
       </c>
       <c r="J326" s="3" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>14350000</v>
       </c>
       <c r="L326" s="5" t="n">
-        <v>30147</v>
+        <v>30211</v>
       </c>
       <c r="M326" s="3" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         </is>
       </c>
       <c r="E350" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F350" s="3" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>14095000</v>
       </c>
       <c r="I350" s="5" t="n">
-        <v>29611</v>
+        <v>29674</v>
       </c>
       <c r="J350" s="3" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>14095000</v>
       </c>
       <c r="L350" s="5" t="n">
-        <v>29611</v>
+        <v>29674</v>
       </c>
       <c r="M350" s="3" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         </is>
       </c>
       <c r="E366" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>14436000</v>
       </c>
       <c r="I366" s="5" t="n">
-        <v>30328</v>
+        <v>30392</v>
       </c>
       <c r="J366" s="3" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>14436000</v>
       </c>
       <c r="L366" s="5" t="n">
-        <v>30328</v>
+        <v>30392</v>
       </c>
       <c r="M366" s="3" t="inlineStr">
         <is>
@@ -23760,7 +23760,7 @@
         </is>
       </c>
       <c r="E374" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F374" s="3" t="inlineStr">
         <is>
@@ -23776,7 +23776,7 @@
         <v>14181000</v>
       </c>
       <c r="I374" s="5" t="n">
-        <v>29792</v>
+        <v>29855</v>
       </c>
       <c r="J374" s="3" t="inlineStr">
         <is>
@@ -23787,7 +23787,7 @@
         <v>14181000</v>
       </c>
       <c r="L374" s="5" t="n">
-        <v>29792</v>
+        <v>29855</v>
       </c>
       <c r="M374" s="3" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         </is>
       </c>
       <c r="E378" s="4" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F378" s="3" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>14223000</v>
       </c>
       <c r="I378" s="5" t="n">
-        <v>29880</v>
+        <v>29943</v>
       </c>
       <c r="J378" s="3" t="inlineStr">
         <is>
@@ -24035,7 +24035,7 @@
         <v>14223000</v>
       </c>
       <c r="L378" s="5" t="n">
-        <v>29880</v>
+        <v>29943</v>
       </c>
       <c r="M378" s="3" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         </is>
       </c>
       <c r="E383" s="4" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F383" s="3" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>7274000</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>25083</v>
+        <v>25170</v>
       </c>
       <c r="J383" s="3" t="inlineStr">
         <is>
@@ -24345,7 +24345,7 @@
         <v>7274000</v>
       </c>
       <c r="L383" s="5" t="n">
-        <v>25083</v>
+        <v>25170</v>
       </c>
       <c r="M383" s="3" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         </is>
       </c>
       <c r="E388" s="4" t="n">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="F388" s="3" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>48737000</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>43710</v>
+        <v>43907</v>
       </c>
       <c r="J388" s="3" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>48737000</v>
       </c>
       <c r="L388" s="5" t="n">
-        <v>43710</v>
+        <v>43907</v>
       </c>
       <c r="M388" s="3" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         </is>
       </c>
       <c r="E408" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F408" s="3" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>29380000</v>
       </c>
       <c r="I408" s="5" t="n">
-        <v>38405</v>
+        <v>38355</v>
       </c>
       <c r="J408" s="3" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>29380000</v>
       </c>
       <c r="L408" s="5" t="n">
-        <v>38405</v>
+        <v>38355</v>
       </c>
       <c r="M408" s="3" t="inlineStr">
         <is>
@@ -26364,7 +26364,7 @@
         </is>
       </c>
       <c r="E416" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F416" s="3" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>28918000</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>37801</v>
+        <v>37752</v>
       </c>
       <c r="J416" s="3" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>28918000</v>
       </c>
       <c r="L416" s="5" t="n">
-        <v>37801</v>
+        <v>37752</v>
       </c>
       <c r="M416" s="3" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         </is>
       </c>
       <c r="E417" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F417" s="3" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>18225000</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>37270</v>
+        <v>37346</v>
       </c>
       <c r="J417" s="3" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>18225000</v>
       </c>
       <c r="L417" s="5" t="n">
-        <v>37270</v>
+        <v>37346</v>
       </c>
       <c r="M417" s="3" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="E424" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F424" s="3" t="inlineStr">
         <is>
@@ -26876,7 +26876,7 @@
         <v>20576000</v>
       </c>
       <c r="I424" s="5" t="n">
-        <v>26897</v>
+        <v>26862</v>
       </c>
       <c r="J424" s="3" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>20576000</v>
       </c>
       <c r="L424" s="5" t="n">
-        <v>26897</v>
+        <v>26862</v>
       </c>
       <c r="M424" s="3" t="inlineStr">
         <is>
@@ -26922,7 +26922,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -26938,7 +26938,7 @@
         <v>17512000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>35812</v>
+        <v>35885</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>17512000</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>35812</v>
+        <v>35885</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="E433" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F433" s="3" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>13371000</v>
       </c>
       <c r="I433" s="5" t="n">
-        <v>27344</v>
+        <v>27400</v>
       </c>
       <c r="J433" s="3" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>13371000</v>
       </c>
       <c r="L433" s="5" t="n">
-        <v>27344</v>
+        <v>27400</v>
       </c>
       <c r="M433" s="3" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
@@ -28426,7 +28426,7 @@
         <v>13265000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>27127</v>
+        <v>27182</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>13265000</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>27127</v>
+        <v>27182</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="E457" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F457" s="3" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>13212000</v>
       </c>
       <c r="I457" s="5" t="n">
-        <v>27018</v>
+        <v>27074</v>
       </c>
       <c r="J457" s="3" t="inlineStr">
         <is>
@@ -28933,7 +28933,7 @@
         <v>13212000</v>
       </c>
       <c r="L457" s="5" t="n">
-        <v>27018</v>
+        <v>27074</v>
       </c>
       <c r="M457" s="3" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         </is>
       </c>
       <c r="E464" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F464" s="3" t="inlineStr">
         <is>
@@ -29356,7 +29356,7 @@
         <v>27235000</v>
       </c>
       <c r="I464" s="5" t="n">
-        <v>35601</v>
+        <v>35555</v>
       </c>
       <c r="J464" s="3" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>27235000</v>
       </c>
       <c r="L464" s="5" t="n">
-        <v>35601</v>
+        <v>35555</v>
       </c>
       <c r="M464" s="3" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>13159000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>26910</v>
+        <v>26965</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -29429,7 +29429,7 @@
         <v>13159000</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>26910</v>
+        <v>26965</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -29836,7 +29836,7 @@
         </is>
       </c>
       <c r="E472" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>23200000</v>
       </c>
       <c r="I472" s="5" t="n">
-        <v>30327</v>
+        <v>30287</v>
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
@@ -29863,7 +29863,7 @@
         <v>23200000</v>
       </c>
       <c r="L472" s="5" t="n">
-        <v>30327</v>
+        <v>30287</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
@@ -30394,7 +30394,7 @@
         </is>
       </c>
       <c r="E481" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F481" s="3" t="inlineStr">
         <is>
@@ -30410,7 +30410,7 @@
         <v>13048000</v>
       </c>
       <c r="I481" s="5" t="n">
-        <v>26683</v>
+        <v>26738</v>
       </c>
       <c r="J481" s="3" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>13048000</v>
       </c>
       <c r="L481" s="5" t="n">
-        <v>26683</v>
+        <v>26738</v>
       </c>
       <c r="M481" s="3" t="inlineStr">
         <is>
@@ -31324,7 +31324,7 @@
         </is>
       </c>
       <c r="E496" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F496" s="3" t="inlineStr">
         <is>
@@ -31340,7 +31340,7 @@
         <v>27674000</v>
       </c>
       <c r="I496" s="5" t="n">
-        <v>36175</v>
+        <v>36128</v>
       </c>
       <c r="J496" s="3" t="inlineStr">
         <is>
@@ -31351,7 +31351,7 @@
         <v>27674000</v>
       </c>
       <c r="L496" s="5" t="n">
-        <v>36175</v>
+        <v>36128</v>
       </c>
       <c r="M496" s="3" t="inlineStr">
         <is>
@@ -31882,7 +31882,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -31898,7 +31898,7 @@
         <v>12892000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>26364</v>
+        <v>26418</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -31909,7 +31909,7 @@
         <v>12892000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>26364</v>
+        <v>26418</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         </is>
       </c>
       <c r="E512" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F512" s="3" t="inlineStr">
         <is>
@@ -32332,7 +32332,7 @@
         <v>23209000</v>
       </c>
       <c r="I512" s="5" t="n">
-        <v>30339</v>
+        <v>30299</v>
       </c>
       <c r="J512" s="3" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>23209000</v>
       </c>
       <c r="L512" s="5" t="n">
-        <v>30339</v>
+        <v>30299</v>
       </c>
       <c r="M512" s="3" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         </is>
       </c>
       <c r="E513" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F513" s="3" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>12841000</v>
       </c>
       <c r="I513" s="5" t="n">
-        <v>26260</v>
+        <v>26314</v>
       </c>
       <c r="J513" s="3" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>12841000</v>
       </c>
       <c r="L513" s="5" t="n">
-        <v>26260</v>
+        <v>26314</v>
       </c>
       <c r="M513" s="3" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         </is>
       </c>
       <c r="E521" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F521" s="3" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>16710000</v>
       </c>
       <c r="I521" s="5" t="n">
-        <v>34172</v>
+        <v>34242</v>
       </c>
       <c r="J521" s="3" t="inlineStr">
         <is>
@@ -32901,7 +32901,7 @@
         <v>16710000</v>
       </c>
       <c r="L521" s="5" t="n">
-        <v>34172</v>
+        <v>34242</v>
       </c>
       <c r="M521" s="3" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         </is>
       </c>
       <c r="E537" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>17218000</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>35211</v>
+        <v>35283</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>17218000</v>
       </c>
       <c r="L537" s="5" t="n">
-        <v>35211</v>
+        <v>35283</v>
       </c>
       <c r="M537" s="3" t="inlineStr">
         <is>
@@ -34362,7 +34362,7 @@
         </is>
       </c>
       <c r="E545" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>17218000</v>
       </c>
       <c r="I545" s="5" t="n">
-        <v>35211</v>
+        <v>35283</v>
       </c>
       <c r="J545" s="3" t="inlineStr">
         <is>
@@ -34389,7 +34389,7 @@
         <v>17218000</v>
       </c>
       <c r="L545" s="5" t="n">
-        <v>35211</v>
+        <v>35283</v>
       </c>
       <c r="M545" s="3" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         </is>
       </c>
       <c r="E552" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>24697000</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>32284</v>
+        <v>32242</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -34823,7 +34823,7 @@
         <v>24697000</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>32284</v>
+        <v>32242</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         </is>
       </c>
       <c r="E560" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F560" s="3" t="inlineStr">
         <is>
@@ -35308,7 +35308,7 @@
         <v>24405000</v>
       </c>
       <c r="I560" s="5" t="n">
-        <v>31902</v>
+        <v>31860</v>
       </c>
       <c r="J560" s="3" t="inlineStr">
         <is>
@@ -35319,7 +35319,7 @@
         <v>24405000</v>
       </c>
       <c r="L560" s="5" t="n">
-        <v>31902</v>
+        <v>31860</v>
       </c>
       <c r="M560" s="3" t="inlineStr">
         <is>
@@ -35850,7 +35850,7 @@
         </is>
       </c>
       <c r="E569" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F569" s="3" t="inlineStr">
         <is>
@@ -35866,7 +35866,7 @@
         <v>16413000</v>
       </c>
       <c r="I569" s="5" t="n">
-        <v>33564</v>
+        <v>33633</v>
       </c>
       <c r="J569" s="3" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>16413000</v>
       </c>
       <c r="L569" s="5" t="n">
-        <v>33564</v>
+        <v>33633</v>
       </c>
       <c r="M569" s="3" t="inlineStr">
         <is>
@@ -36842,7 +36842,7 @@
         </is>
       </c>
       <c r="E585" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>16314000</v>
       </c>
       <c r="I585" s="5" t="n">
-        <v>33362</v>
+        <v>33430</v>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>16314000</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>33362</v>
+        <v>33430</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         </is>
       </c>
       <c r="E592" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F592" s="3" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>24257000</v>
       </c>
       <c r="I592" s="5" t="n">
-        <v>31708</v>
+        <v>31667</v>
       </c>
       <c r="J592" s="3" t="inlineStr">
         <is>
@@ -37303,7 +37303,7 @@
         <v>24257000</v>
       </c>
       <c r="L592" s="5" t="n">
-        <v>31708</v>
+        <v>31667</v>
       </c>
       <c r="M592" s="3" t="inlineStr">
         <is>
@@ -37338,7 +37338,7 @@
         </is>
       </c>
       <c r="E593" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F593" s="3" t="inlineStr">
         <is>
@@ -37354,7 +37354,7 @@
         <v>12426000</v>
       </c>
       <c r="I593" s="5" t="n">
-        <v>25411</v>
+        <v>25463</v>
       </c>
       <c r="J593" s="3" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>12426000</v>
       </c>
       <c r="L593" s="5" t="n">
-        <v>25411</v>
+        <v>25463</v>
       </c>
       <c r="M593" s="3" t="inlineStr">
         <is>
@@ -37772,7 +37772,7 @@
         </is>
       </c>
       <c r="E600" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F600" s="3" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>24185000</v>
       </c>
       <c r="I600" s="5" t="n">
-        <v>31614</v>
+        <v>31573</v>
       </c>
       <c r="J600" s="3" t="inlineStr">
         <is>
@@ -37799,7 +37799,7 @@
         <v>24185000</v>
       </c>
       <c r="L600" s="5" t="n">
-        <v>31614</v>
+        <v>31573</v>
       </c>
       <c r="M600" s="3" t="inlineStr">
         <is>
@@ -37834,7 +37834,7 @@
         </is>
       </c>
       <c r="E601" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F601" s="3" t="inlineStr">
         <is>
@@ -37850,7 +37850,7 @@
         <v>12389000</v>
       </c>
       <c r="I601" s="5" t="n">
-        <v>25335</v>
+        <v>25387</v>
       </c>
       <c r="J601" s="3" t="inlineStr">
         <is>
@@ -37861,7 +37861,7 @@
         <v>12389000</v>
       </c>
       <c r="L601" s="5" t="n">
-        <v>25335</v>
+        <v>25387</v>
       </c>
       <c r="M601" s="3" t="inlineStr">
         <is>
@@ -38330,7 +38330,7 @@
         </is>
       </c>
       <c r="E609" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F609" s="3" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>12389000</v>
       </c>
       <c r="I609" s="5" t="n">
-        <v>25335</v>
+        <v>25387</v>
       </c>
       <c r="J609" s="3" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>12389000</v>
       </c>
       <c r="L609" s="5" t="n">
-        <v>25335</v>
+        <v>25387</v>
       </c>
       <c r="M609" s="3" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         </is>
       </c>
       <c r="E616" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F616" s="3" t="inlineStr">
         <is>
@@ -38780,7 +38780,7 @@
         <v>23261000</v>
       </c>
       <c r="I616" s="5" t="n">
-        <v>30407</v>
+        <v>30367</v>
       </c>
       <c r="J616" s="3" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>23261000</v>
       </c>
       <c r="L616" s="5" t="n">
-        <v>30407</v>
+        <v>30367</v>
       </c>
       <c r="M616" s="3" t="inlineStr">
         <is>
@@ -38826,7 +38826,7 @@
         </is>
       </c>
       <c r="E617" s="4" t="n">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F617" s="3" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>12315000</v>
       </c>
       <c r="I617" s="5" t="n">
-        <v>25184</v>
+        <v>25236</v>
       </c>
       <c r="J617" s="3" t="inlineStr">
         <is>
@@ -38853,7 +38853,7 @@
         <v>12315000</v>
       </c>
       <c r="L617" s="5" t="n">
-        <v>25184</v>
+        <v>25236</v>
       </c>
       <c r="M617" s="3" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         </is>
       </c>
       <c r="E637" s="4" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="F637" s="3" t="inlineStr">
         <is>
@@ -40082,7 +40082,7 @@
         <v>17031000</v>
       </c>
       <c r="I637" s="5" t="n">
-        <v>29774</v>
+        <v>29827</v>
       </c>
       <c r="J637" s="3" t="inlineStr">
         <is>
@@ -40093,7 +40093,7 @@
         <v>17031000</v>
       </c>
       <c r="L637" s="5" t="n">
-        <v>29774</v>
+        <v>29827</v>
       </c>
       <c r="M637" s="3" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         </is>
       </c>
       <c r="E640" s="4" t="n">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F640" s="3" t="inlineStr">
         <is>
@@ -40268,7 +40268,7 @@
         <v>24020000</v>
       </c>
       <c r="I640" s="5" t="n">
-        <v>31399</v>
+        <v>31358</v>
       </c>
       <c r="J640" s="3" t="inlineStr">
         <is>
@@ -40279,7 +40279,7 @@
         <v>24020000</v>
       </c>
       <c r="L640" s="5" t="n">
-        <v>31399</v>
+        <v>31358</v>
       </c>
       <c r="M640" s="3" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         </is>
       </c>
       <c r="E641" s="4" t="n">
-        <v>1067</v>
+        <v>1057</v>
       </c>
       <c r="F641" s="3" t="inlineStr">
         <is>
@@ -40330,7 +40330,7 @@
         <v>47000000</v>
       </c>
       <c r="I641" s="5" t="n">
-        <v>44049</v>
+        <v>44465</v>
       </c>
       <c r="J641" s="3" t="inlineStr">
         <is>
@@ -40341,7 +40341,7 @@
         <v>47000000</v>
       </c>
       <c r="L641" s="5" t="n">
-        <v>44049</v>
+        <v>44465</v>
       </c>
       <c r="M641" s="3" t="inlineStr">
         <is>
@@ -40376,7 +40376,7 @@
         </is>
       </c>
       <c r="E642" s="4" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F642" s="3" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>33508000</v>
       </c>
       <c r="I642" s="5" t="n">
-        <v>34687</v>
+        <v>34723</v>
       </c>
       <c r="J642" s="3" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>33508000</v>
       </c>
       <c r="L642" s="5" t="n">
-        <v>34687</v>
+        <v>34723</v>
       </c>
       <c r="M642" s="3" t="inlineStr">
         <is>
@@ -40632,7 +40632,7 @@
         </is>
       </c>
       <c r="E646" s="4" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F646" s="3" t="inlineStr">
         <is>
@@ -40648,7 +40648,7 @@
         <v>43634000</v>
       </c>
       <c r="I646" s="5" t="n">
-        <v>33539</v>
+        <v>33513</v>
       </c>
       <c r="J646" s="3" t="inlineStr">
         <is>
@@ -40659,7 +40659,7 @@
         <v>43634000</v>
       </c>
       <c r="L646" s="5" t="n">
-        <v>33539</v>
+        <v>33513</v>
       </c>
       <c r="M646" s="3" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         </is>
       </c>
       <c r="E648" s="4" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F648" s="3" t="inlineStr">
         <is>
@@ -40772,7 +40772,7 @@
         <v>32747000</v>
       </c>
       <c r="I648" s="5" t="n">
-        <v>33900</v>
+        <v>33935</v>
       </c>
       <c r="J648" s="3" t="inlineStr">
         <is>
@@ -40783,7 +40783,7 @@
         <v>32747000</v>
       </c>
       <c r="L648" s="5" t="n">
-        <v>33900</v>
+        <v>33935</v>
       </c>
       <c r="M648" s="3" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         </is>
       </c>
       <c r="E649" s="4" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F649" s="3" t="inlineStr">
         <is>
@@ -40834,7 +40834,7 @@
         <v>43400000</v>
       </c>
       <c r="I649" s="5" t="n">
-        <v>33359</v>
+        <v>33333</v>
       </c>
       <c r="J649" s="3" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>43400000</v>
       </c>
       <c r="L649" s="5" t="n">
-        <v>33359</v>
+        <v>33333</v>
       </c>
       <c r="M649" s="3" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         </is>
       </c>
       <c r="E651" s="4" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F651" s="3" t="inlineStr">
         <is>
@@ -40958,7 +40958,7 @@
         <v>32422000</v>
       </c>
       <c r="I651" s="5" t="n">
-        <v>33563</v>
+        <v>33598</v>
       </c>
       <c r="J651" s="3" t="inlineStr">
         <is>
@@ -40969,7 +40969,7 @@
         <v>32422000</v>
       </c>
       <c r="L651" s="5" t="n">
-        <v>33563</v>
+        <v>33598</v>
       </c>
       <c r="M651" s="3" t="inlineStr">
         <is>
@@ -41004,7 +41004,7 @@
         </is>
       </c>
       <c r="E652" s="4" t="n">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F652" s="3" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>44700800</v>
       </c>
       <c r="I652" s="5" t="n">
-        <v>34359</v>
+        <v>34332</v>
       </c>
       <c r="J652" s="3" t="inlineStr">
         <is>
@@ -41031,7 +41031,7 @@
         <v>44700800</v>
       </c>
       <c r="L652" s="5" t="n">
-        <v>34359</v>
+        <v>34332</v>
       </c>
       <c r="M652" s="3" t="inlineStr">
         <is>
@@ -50523,13 +50523,57 @@
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
         <is>
+          <t>41&amp;42</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>A | 2084呎 (4+房)
+$11000万
+$52,783/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>B | 1284呎 (4+房)
+$5406万
+$42,105/呎
+(26年-01月-02日)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 1285呎 (4+房)
+$5500万
+$42,802/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr"/>
+      <c r="F6" s="20" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 1867呎 (4+房)
+$9580万
+$51,312/呎
+(24年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr"/>
+      <c r="I6" s="20" t="inlineStr"/>
+      <c r="J6" s="20" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="20" t="inlineStr"/>
-      <c r="E6" s="21" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 389呎 (1房)
 $1388万
@@ -50537,7 +50581,7 @@
 (21年-05月-27日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t>E | 572呎 (2房)
 $2009万
@@ -50545,8 +50589,8 @@
 (21年-06月-02日)</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
-      <c r="H6" s="21" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>G | 850呎 (3房)
 $3362万
@@ -50554,50 +50598,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I6" s="20" t="inlineStr"/>
-      <c r="J6" s="20" t="inlineStr"/>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41&amp;42</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>A | 2095呎 (4+房)
-$11000万
-$52,506/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr">
-        <is>
-          <t>B | 1294呎 (4+房)
-$5406万
-$41,780/呎
-(26年-01月-02日)</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>C | 1294呎 (4+房)
-$5500万
-$42,504/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>F | 1866呎 (4+房)
-$9580万
-$51,340/呎
-(24年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr"/>
       <c r="I7" s="20" t="inlineStr"/>
       <c r="J7" s="20" t="inlineStr"/>
     </row>
@@ -50609,9 +50609,9 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1206呎 (4+房)
+          <t>A | 1205呎 (4+房)
 $5664万
-$46,961/呎
+$47,000/呎
 (21年-09月-24日)</t>
         </is>
       </c>
@@ -50690,9 +50690,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 1206呎 (4+房)
+          <t>A | 1205呎 (4+房)
 $5422万
-$44,963/呎
+$45,000/呎
 (21年-05月-18日)</t>
         </is>
       </c>
@@ -50741,9 +50741,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 1206呎 (4+房)
+          <t>A | 1205呎 (4+房)
 $5302万
-$43,964/呎
+$44,000/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -50787,20 +50787,50 @@
     <row r="12" ht="58" customHeight="1">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>37&amp;38</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4222万
+$32,678/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4220万
+$32,663/呎
+(25年-03月-14日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
+      <c r="F12" s="20" t="inlineStr"/>
+      <c r="G12" s="20" t="inlineStr"/>
+      <c r="H12" s="20" t="inlineStr"/>
+      <c r="I12" s="20" t="inlineStr"/>
+      <c r="J12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
 $5434万
-$45,054/呎
+$45,091/呎
 (21年-06月-17日)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr"/>
-      <c r="E12" s="21" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr"/>
+      <c r="D13" s="20" t="inlineStr"/>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1321万
@@ -50808,15 +50838,15 @@
 (21年-05月-01日)</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
 $1822万
-$31,803/呎
+$31,858/呎
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5288万
@@ -50824,7 +50854,7 @@
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="H12" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $3102万
@@ -50832,36 +50862,6 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="I12" s="20" t="inlineStr"/>
-      <c r="J12" s="20" t="inlineStr"/>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>37&amp;38</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr"/>
-      <c r="C13" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4222万
-$32,678/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4220万
-$32,663/呎
-(25年-03月-14日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-      <c r="F13" s="20" t="inlineStr"/>
-      <c r="G13" s="20" t="inlineStr"/>
-      <c r="H13" s="20" t="inlineStr"/>
       <c r="I13" s="20" t="inlineStr"/>
       <c r="J13" s="20" t="inlineStr"/>
     </row>
@@ -50891,9 +50891,9 @@
       </c>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 572呎 (2房)
 $1817万
-$31,707/呎
+$31,762/呎
 (21年-05月-28日)</t>
         </is>
       </c>
@@ -50919,11 +50919,62 @@
     <row r="15" ht="58" customHeight="1">
       <c r="A15" s="19" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5246万
+$43,537/呎
+(21年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr"/>
+      <c r="D15" s="20" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1314万
+$34,308/呎
+(21年-05月-17日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1878万
+$32,827/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$5176万
+$42,500/呎
+(21年-06月-07日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3071万
+$36,560/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr"/>
+      <c r="J15" s="20" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
           <t>35&amp;36</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr"/>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4570万
@@ -50931,7 +50982,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4335万
@@ -50939,61 +50990,10 @@
 (25年-03月-12日)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr"/>
-      <c r="F15" s="20" t="inlineStr"/>
-      <c r="G15" s="20" t="inlineStr"/>
-      <c r="H15" s="20" t="inlineStr"/>
-      <c r="I15" s="20" t="inlineStr"/>
-      <c r="J15" s="20" t="inlineStr"/>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5246万
-$43,537/呎
-(21年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr"/>
-      <c r="D16" s="20" t="inlineStr"/>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1314万
-$34,308/呎
-(21年-05月-17日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1878万
-$32,770/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$5176万
-$42,500/呎
-(21年-06月-07日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3071万
-$36,560/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
+      <c r="E16" s="20" t="inlineStr"/>
+      <c r="F16" s="20" t="inlineStr"/>
+      <c r="G16" s="20" t="inlineStr"/>
+      <c r="H16" s="20" t="inlineStr"/>
       <c r="I16" s="20" t="inlineStr"/>
       <c r="J16" s="20" t="inlineStr"/>
     </row>
@@ -51051,11 +51051,62 @@
     <row r="18" ht="58" customHeight="1">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$5000万
+$41,492/呎
+(23年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1292万
+$33,736/呎
+(21年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1848万
+$32,316/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$4820万
+$39,571/呎
+(24年-11月-05日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$3152万
+$37,521/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr"/>
+      <c r="J18" s="20" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>32&amp;33</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr"/>
-      <c r="C18" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4190万
@@ -51063,7 +51114,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $4133万
@@ -51071,61 +51122,10 @@
 (25年-01月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr"/>
-      <c r="F18" s="20" t="inlineStr"/>
-      <c r="G18" s="20" t="inlineStr"/>
-      <c r="H18" s="20" t="inlineStr"/>
-      <c r="I18" s="20" t="inlineStr"/>
-      <c r="J18" s="20" t="inlineStr"/>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>A | 1205呎 (4+房)
-$5000万
-$41,492/呎
-(23年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr"/>
-      <c r="D19" s="20" t="inlineStr"/>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1292万
-$33,736/呎
-(21年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
-$1848万
-$32,260/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$4820万
-$39,571/呎
-(24年-11月-05日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$3152万
-$37,521/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
+      <c r="E19" s="20" t="inlineStr"/>
+      <c r="F19" s="20" t="inlineStr"/>
+      <c r="G19" s="20" t="inlineStr"/>
+      <c r="H19" s="20" t="inlineStr"/>
       <c r="I19" s="20" t="inlineStr"/>
       <c r="J19" s="20" t="inlineStr"/>
     </row>
@@ -51155,9 +51155,9 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 572呎 (2房)
 $1604万
-$28,002/呎
+$28,051/呎
 (24年-01月-12日)</t>
         </is>
       </c>
@@ -51183,20 +51183,50 @@
     <row r="21" ht="58" customHeight="1">
       <c r="A21" s="19" t="inlineStr">
         <is>
+          <t>30&amp;31</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4278万
+$33,111/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4076万
+$31,545/呎
+(25年-01月-10日)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr"/>
+      <c r="F21" s="20" t="inlineStr"/>
+      <c r="G21" s="20" t="inlineStr"/>
+      <c r="H21" s="20" t="inlineStr"/>
+      <c r="I21" s="20" t="inlineStr"/>
+      <c r="J21" s="20" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
 $4880万
-$40,466/呎
+$40,500/呎
 (21年-07月-15日)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr"/>
-      <c r="D21" s="20" t="inlineStr"/>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1255万
@@ -51204,15 +51234,15 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
 $1773万
-$30,935/呎
+$30,990/呎
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3992万
@@ -51220,7 +51250,7 @@
 (24年-09月-25日)</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2867万
@@ -51228,36 +51258,6 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr"/>
-      <c r="J21" s="20" t="inlineStr"/>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>30&amp;31</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4278万
-$33,111/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4076万
-$31,545/呎
-(25年-01月-10日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr"/>
-      <c r="F22" s="20" t="inlineStr"/>
-      <c r="G22" s="20" t="inlineStr"/>
-      <c r="H22" s="20" t="inlineStr"/>
       <c r="I22" s="20" t="inlineStr"/>
       <c r="J22" s="20" t="inlineStr"/>
     </row>
@@ -51269,9 +51269,9 @@
       </c>
       <c r="B23" s="21" t="inlineStr">
         <is>
-          <t>A | 1206呎 (4+房)
+          <t>A | 1205呎 (4+房)
 $5278万
-$43,764/呎
+$43,800/呎
 (21年-05月-20日)</t>
         </is>
       </c>
@@ -51287,9 +51287,9 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 572呎 (2房)
 $1595万
-$27,834/呎
+$27,883/呎
 (24年-02月-06日)</t>
         </is>
       </c>
@@ -51315,20 +51315,50 @@
     <row r="24" ht="58" customHeight="1">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>28&amp;29</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4091万
+$31,666/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$4039万
+$31,260/呎
+(25年-04月-28日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr"/>
+      <c r="F24" s="20" t="inlineStr"/>
+      <c r="G24" s="20" t="inlineStr"/>
+      <c r="H24" s="20" t="inlineStr"/>
+      <c r="I24" s="20" t="inlineStr"/>
+      <c r="J24" s="20" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
 $5018万
-$41,609/呎
+$41,643/呎
 (21年-06月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr"/>
-      <c r="D24" s="20" t="inlineStr"/>
-      <c r="E24" s="21" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr"/>
+      <c r="D25" s="20" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1298万
@@ -51336,15 +51366,15 @@
 (21年-05月-24日)</t>
         </is>
       </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
 $1595万
-$27,834/呎
+$27,883/呎
 (24年-03月-21日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $5000万
@@ -51352,7 +51382,7 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="H24" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2957万
@@ -51360,36 +51390,6 @@
 (21年-05月-25日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr"/>
-      <c r="J24" s="20" t="inlineStr"/>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>28&amp;29</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr"/>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4091万
-$31,666/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$4039万
-$31,260/呎
-(25年-04月-28日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr"/>
-      <c r="F25" s="20" t="inlineStr"/>
-      <c r="G25" s="20" t="inlineStr"/>
-      <c r="H25" s="20" t="inlineStr"/>
       <c r="I25" s="20" t="inlineStr"/>
       <c r="J25" s="20" t="inlineStr"/>
     </row>
@@ -51419,9 +51419,9 @@
       </c>
       <c r="F26" s="21" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 572呎 (2房)
 $1585万
-$27,668/呎
+$27,717/呎
 (24年-04月-05日)</t>
         </is>
       </c>
@@ -51447,20 +51447,50 @@
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
+          <t>26&amp;27</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>B | 1292呎 (4+房)
+$4630万
+$35,836/呎
+(23年-06月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
+        <is>
+          <t>C | 1292呎 (4+房)
+$3998万
+$30,947/呎
+(24年-11月-14日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr"/>
+      <c r="F27" s="20" t="inlineStr"/>
+      <c r="G27" s="20" t="inlineStr"/>
+      <c r="H27" s="20" t="inlineStr"/>
+      <c r="I27" s="20" t="inlineStr"/>
+      <c r="J27" s="20" t="inlineStr"/>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
 $4840万
-$40,137/呎
+$40,170/呎
 (21年-05月-26日)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr"/>
-      <c r="D27" s="20" t="inlineStr"/>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr"/>
+      <c r="D28" s="20" t="inlineStr"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 383呎 (1房)
 $1288万
@@ -51468,15 +51498,15 @@
 (21年-05月-17日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 573呎 (2房)
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
 $1789万
-$31,220/呎
+$31,274/呎
 (21年-05月-20日)</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 1218呎 (4+房)
 $3664万
@@ -51484,7 +51514,7 @@
 (24年-10月-18日)</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 840呎 (3房)
 $2810万
@@ -51492,36 +51522,6 @@
 (21年-05月-18日)</t>
         </is>
       </c>
-      <c r="I27" s="20" t="inlineStr"/>
-      <c r="J27" s="20" t="inlineStr"/>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>26&amp;27</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr"/>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>B | 1292呎 (4+房)
-$4630万
-$35,836/呎
-(23年-06月-21日)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 1292呎 (4+房)
-$3998万
-$30,947/呎
-(24年-11月-14日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr"/>
-      <c r="F28" s="20" t="inlineStr"/>
-      <c r="G28" s="20" t="inlineStr"/>
-      <c r="H28" s="20" t="inlineStr"/>
       <c r="I28" s="20" t="inlineStr"/>
       <c r="J28" s="20" t="inlineStr"/>
     </row>
@@ -51579,11 +51579,62 @@
     <row r="30" ht="58" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>A | 1205呎 (4+房)
+$3988万
+$33,095/呎
+(24年-02月-01日)</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="21" t="inlineStr">
+        <is>
+          <t>D | 383呎 (1房)
+$1236万
+$32,282/呎
+(21年-05月-25日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>E | 572呎 (2房)
+$1726万
+$30,168/呎
+(21年-05月-14日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
+        <is>
+          <t>F | 1218呎 (4+房)
+$3600万
+$29,556/呎
+(24年-11月-07日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 840呎 (3房)
+$2783万
+$33,126/呎
+(21年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="I30" s="20" t="inlineStr"/>
+      <c r="J30" s="20" t="inlineStr"/>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
           <t>23&amp;25</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr"/>
-      <c r="C30" s="21" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>B | 1292呎 (4+房)
 $4365万
@@ -51591,7 +51642,7 @@
 (24年-05月-03日)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 1292呎 (4+房)
 $3948万
@@ -51599,61 +51650,10 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="E30" s="20" t="inlineStr"/>
-      <c r="F30" s="20" t="inlineStr"/>
-      <c r="G30" s="20" t="inlineStr"/>
-      <c r="H30" s="20" t="inlineStr"/>
-      <c r="I30" s="20" t="inlineStr"/>
-      <c r="J30" s="20" t="inlineStr"/>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>A | 1206呎 (4+房)
-$3988万
-$33,068/呎
-(24年-02月-01日)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr"/>
-      <c r="D31" s="20" t="inlineStr"/>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 383呎 (1房)
-$1236万
-$32,282/呎
-(21年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 572呎 (2房)
-$1726万
-$30,168/呎
-(21年-05月-14日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 1218呎 (4+房)
-$3600万
-$29,556/呎
-(24年-11月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 840呎 (3房)
-$2783万
-$33,126/呎
-(21年-05月-18日)</t>
-        </is>
-      </c>
+      <c r="E31" s="20" t="inlineStr"/>
+      <c r="F31" s="20" t="inlineStr"/>
+      <c r="G31" s="20" t="inlineStr"/>
+      <c r="H31" s="20" t="inlineStr"/>
       <c r="I31" s="20" t="inlineStr"/>
       <c r="J31" s="20" t="inlineStr"/>
     </row>
@@ -51697,9 +51697,9 @@
       </c>
       <c r="F32" s="21" t="inlineStr">
         <is>
-          <t>E | 573呎 (2房)
+          <t>E | 572呎 (2房)
 $1783万
-$31,122/呎
+$31,177/呎
 (21年-05月-20日)</t>
         </is>
       </c>
@@ -51730,9 +51730,9 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $4234万
-$37,267/呎
+$37,300/呎
 (21年-11月-11日)</t>
         </is>
       </c>
@@ -51770,9 +51770,9 @@
       </c>
       <c r="G33" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2727万
-$29,071/呎
+$29,102/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -51794,9 +51794,9 @@
       </c>
       <c r="J33" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1263万
-$32,718/呎
+$32,633/呎
 (21年-05月-31日)</t>
         </is>
       </c>
@@ -51849,9 +51849,9 @@
       </c>
       <c r="G34" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2623万
-$27,962/呎
+$27,991/呎
 (21年-05月-21日)</t>
         </is>
       </c>
@@ -51873,9 +51873,9 @@
       </c>
       <c r="J34" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1215万
-$31,469/呎
+$31,388/呎
 (21年-06月-04日)</t>
         </is>
       </c>
@@ -51888,9 +51888,9 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $4143万
-$36,468/呎
+$36,500/呎
 (21年-06月-18日)</t>
         </is>
       </c>
@@ -51928,9 +51928,9 @@
       </c>
       <c r="G35" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2615万
-$27,878/呎
+$27,908/呎
 (21年-05月-21日)</t>
         </is>
       </c>
@@ -51952,9 +51952,9 @@
       </c>
       <c r="J35" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1255万
-$32,521/呎
+$32,437/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -52007,9 +52007,9 @@
       </c>
       <c r="G36" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2624万
-$27,970/呎
+$28,000/呎
 (23年-12月-14日)</t>
         </is>
       </c>
@@ -52031,9 +52031,9 @@
       </c>
       <c r="J36" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1248万
-$32,329/呎
+$32,245/呎
 (21年-06月-04日)</t>
         </is>
       </c>
@@ -52125,9 +52125,9 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $4105万
-$36,136/呎
+$36,167/呎
 (21年-06月-07日)</t>
         </is>
       </c>
@@ -52165,9 +52165,9 @@
       </c>
       <c r="G38" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2686万
-$28,640/呎
+$28,670/呎
 (21年-05月-20日)</t>
         </is>
       </c>
@@ -52204,9 +52204,9 @@
       </c>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $3948万
-$34,755/呎
+$34,786/呎
 (21年-06月-07日)</t>
         </is>
       </c>
@@ -52268,9 +52268,9 @@
       </c>
       <c r="J39" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1240万
-$32,137/呎
+$32,054/呎
 (21年-05月-27日)</t>
         </is>
       </c>
@@ -52283,9 +52283,9 @@
       </c>
       <c r="B40" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $4080万
-$35,919/呎
+$35,951/呎
 (21年-05月-15日)</t>
         </is>
       </c>
@@ -52323,9 +52323,9 @@
       </c>
       <c r="G40" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2670万
-$28,469/呎
+$28,499/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -52347,9 +52347,9 @@
       </c>
       <c r="J40" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1237万
-$32,039/呎
+$31,956/呎
 (21年-06月-08日)</t>
         </is>
       </c>
@@ -52426,9 +52426,9 @@
       </c>
       <c r="J41" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $1190万
-$30,816/呎
+$30,736/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -52441,9 +52441,9 @@
       </c>
       <c r="B42" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $4056万
-$35,705/呎
+$35,737/呎
 (21年-06月-04日)</t>
         </is>
       </c>
@@ -52678,9 +52678,9 @@
       </c>
       <c r="B45" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $3798万
-$33,435/呎
+$33,464/呎
 (21年-06月-03日)</t>
         </is>
       </c>
@@ -52742,9 +52742,9 @@
       </c>
       <c r="J45" s="21" t="inlineStr">
         <is>
-          <t>J | 386呎 (1房)
+          <t>J | 387呎 (1房)
 $926万
-$23,995/呎
+$23,933/呎
 (24年-04月-19日)</t>
         </is>
       </c>
@@ -52757,9 +52757,9 @@
       </c>
       <c r="B46" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $3898万
-$34,314/呎
+$34,344/呎
 (21年-06月-07日)</t>
         </is>
       </c>
@@ -52797,9 +52797,9 @@
       </c>
       <c r="G46" s="21" t="inlineStr">
         <is>
-          <t>F | 938呎 (3房)
+          <t>F | 937呎 (3房)
 $2530万
-$26,977/呎
+$27,005/呎
 (21年-05月-25日)</t>
         </is>
       </c>
@@ -52836,9 +52836,9 @@
       </c>
       <c r="B47" s="21" t="inlineStr">
         <is>
-          <t>A | 1136呎 (4+房)
+          <t>A | 1135呎 (4+房)
 $3553万
-$31,272/呎
+$31,300/呎
 (24年-04月-11日)</t>
         </is>
       </c>
@@ -53054,9 +53054,9 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1660万
-$34,876/呎
+$34,949/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -53093,9 +53093,9 @@
       </c>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1628万
-$34,193/呎
+$34,265/呎
 (21年-06月-01日)</t>
         </is>
       </c>
@@ -53132,9 +53132,9 @@
       </c>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1604万
-$33,689/呎
+$33,760/呎
 (21年-05月-31日)</t>
         </is>
       </c>
@@ -53210,9 +53210,9 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1501万
-$31,532/呎
+$31,598/呎
 (21年-05月-01日)</t>
         </is>
       </c>
@@ -53288,9 +53288,9 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1492万
-$31,345/呎
+$31,411/呎
 (21年-05月-14日)</t>
         </is>
       </c>
@@ -53327,9 +53327,9 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1542万
-$32,393/呎
+$32,461/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -53405,9 +53405,9 @@
       </c>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1479万
-$31,063/呎
+$31,128/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -53483,9 +53483,9 @@
       </c>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1203万
-$25,271/呎
+$25,324/呎
 (24年-04月-02日)</t>
         </is>
       </c>
@@ -53600,9 +53600,9 @@
       </c>
       <c r="D19" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1510万
-$31,721/呎
+$31,787/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -53639,9 +53639,9 @@
       </c>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1505万
-$31,626/呎
+$31,693/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -53756,9 +53756,9 @@
       </c>
       <c r="D23" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1439万
-$30,237/呎
+$30,301/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -53795,9 +53795,9 @@
       </c>
       <c r="D24" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1435万
-$30,147/呎
+$30,211/呎
 (21年-05月-18日)</t>
         </is>
       </c>
@@ -54029,9 +54029,9 @@
       </c>
       <c r="D30" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1410万
-$29,611/呎
+$29,674/呎
 (21年-05月-20日)</t>
         </is>
       </c>
@@ -54185,9 +54185,9 @@
       </c>
       <c r="D34" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1444万
-$30,328/呎
+$30,392/呎
 (21年-05月-25日)</t>
         </is>
       </c>
@@ -54263,9 +54263,9 @@
       </c>
       <c r="D36" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1418万
-$29,792/呎
+$29,855/呎
 (21年-05月-27日)</t>
         </is>
       </c>
@@ -54302,9 +54302,9 @@
       </c>
       <c r="D37" s="21" t="inlineStr">
         <is>
-          <t>C | 476呎 (2房)
+          <t>C | 475呎 (2房)
 $1422万
-$29,880/呎
+$29,943/呎
 (21年-06月-02日)</t>
         </is>
       </c>
@@ -54333,9 +54333,9 @@
       </c>
       <c r="C38" s="21" t="inlineStr">
         <is>
-          <t>B | 290呎 (开放式)
+          <t>B | 289呎 (开放式)
 $727万
-$25,083/呎
+$25,170/呎
 (24年-04月-02日)</t>
         </is>
       </c>
@@ -54511,9 +54511,9 @@
       </c>
       <c r="B5" s="21" t="inlineStr">
         <is>
-          <t>A | 1115呎 (3房)
+          <t>A | 1110呎 (3房)
 $4874万
-$43,710/呎
+$43,907/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -54683,9 +54683,9 @@
       </c>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2938万
-$38,405/呎
+$38,355/呎
 (21年-06月-04日)</t>
         </is>
       </c>
@@ -54754,9 +54754,9 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2892万
-$37,801/呎
+$37,752/呎
 (21年-05月-26日)</t>
         </is>
       </c>
@@ -54825,9 +54825,9 @@
       </c>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2058万
-$26,897/呎
+$26,862/呎
 (24年-04月-30日)</t>
         </is>
       </c>
@@ -54881,9 +54881,9 @@
       </c>
       <c r="I11" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1822万
-$37,270/呎
+$37,346/呎
 (21年-06月-11日)</t>
         </is>
       </c>
@@ -54952,9 +54952,9 @@
       </c>
       <c r="I12" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1751万
-$35,812/呎
+$35,885/呎
 (21年-06月-03日)</t>
         </is>
       </c>
@@ -55023,9 +55023,9 @@
       </c>
       <c r="I13" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1337万
-$27,344/呎
+$27,400/呎
 (23年-11月-24日)</t>
         </is>
       </c>
@@ -55165,9 +55165,9 @@
       </c>
       <c r="I15" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1326万
-$27,127/呎
+$27,182/呎
 (24年-03月-03日)</t>
         </is>
       </c>
@@ -55180,9 +55180,9 @@
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2724万
-$35,601/呎
+$35,555/呎
 (21年-05月-26日)</t>
         </is>
       </c>
@@ -55236,9 +55236,9 @@
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1321万
-$27,018/呎
+$27,074/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -55251,9 +55251,9 @@
       </c>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2320万
-$30,327/呎
+$30,287/呎
 (24年-03月-05日)</t>
         </is>
       </c>
@@ -55307,9 +55307,9 @@
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1316万
-$26,910/呎
+$26,965/呎
 (25年-11月-07日)</t>
         </is>
       </c>
@@ -55449,9 +55449,9 @@
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1305万
-$26,683/呎
+$26,738/呎
 (24年-04月-08日)</t>
         </is>
       </c>
@@ -55464,9 +55464,9 @@
       </c>
       <c r="B20" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2767万
-$36,175/呎
+$36,128/呎
 (21年-05月-27日)</t>
         </is>
       </c>
@@ -55606,9 +55606,9 @@
       </c>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2321万
-$30,339/呎
+$30,299/呎
 (24年-04月-03日)</t>
         </is>
       </c>
@@ -55662,9 +55662,9 @@
       </c>
       <c r="I22" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1289万
-$26,364/呎
+$26,418/呎
 (24年-12月-05日)</t>
         </is>
       </c>
@@ -55733,9 +55733,9 @@
       </c>
       <c r="I23" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1284万
-$26,260/呎
+$26,314/呎
 (24年-03月-26日)</t>
         </is>
       </c>
@@ -55804,9 +55804,9 @@
       </c>
       <c r="I24" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1671万
-$34,172/呎
+$34,242/呎
 (21年-09月-28日)</t>
         </is>
       </c>
@@ -55946,9 +55946,9 @@
       </c>
       <c r="I26" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1722万
-$35,211/呎
+$35,283/呎
 (21年-06月-08日)</t>
         </is>
       </c>
@@ -55961,9 +55961,9 @@
       </c>
       <c r="B27" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2470万
-$32,284/呎
+$32,242/呎
 (21年-05月-27日)</t>
         </is>
       </c>
@@ -56017,9 +56017,9 @@
       </c>
       <c r="I27" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1722万
-$35,211/呎
+$35,283/呎
 (21年-06月-03日)</t>
         </is>
       </c>
@@ -56032,9 +56032,9 @@
       </c>
       <c r="B28" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2440万
-$31,902/呎
+$31,860/呎
 (21年-05月-24日)</t>
         </is>
       </c>
@@ -56230,9 +56230,9 @@
       </c>
       <c r="I30" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1641万
-$33,564/呎
+$33,633/呎
 (21年-08月-05日)</t>
         </is>
       </c>
@@ -56316,9 +56316,9 @@
       </c>
       <c r="B32" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2426万
-$31,708/呎
+$31,667/呎
 (21年-06月-02日)</t>
         </is>
       </c>
@@ -56372,9 +56372,9 @@
       </c>
       <c r="I32" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1631万
-$33,362/呎
+$33,430/呎
 (21年-06月-07日)</t>
         </is>
       </c>
@@ -56387,9 +56387,9 @@
       </c>
       <c r="B33" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2418万
-$31,614/呎
+$31,573/呎
 (21年-06月-02日)</t>
         </is>
       </c>
@@ -56443,9 +56443,9 @@
       </c>
       <c r="I33" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1243万
-$25,411/呎
+$25,463/呎
 (24年-03月-28日)</t>
         </is>
       </c>
@@ -56514,9 +56514,9 @@
       </c>
       <c r="I34" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1239万
-$25,335/呎
+$25,387/呎
 (24年-03月-20日)</t>
         </is>
       </c>
@@ -56529,9 +56529,9 @@
       </c>
       <c r="B35" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2326万
-$30,407/呎
+$30,367/呎
 (21年-05月-08日)</t>
         </is>
       </c>
@@ -56585,9 +56585,9 @@
       </c>
       <c r="I35" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1239万
-$25,335/呎
+$25,387/呎
 (24年-03月-26日)</t>
         </is>
       </c>
@@ -56656,9 +56656,9 @@
       </c>
       <c r="I36" s="21" t="inlineStr">
         <is>
-          <t>H | 489呎 (2房)
+          <t>H | 488呎 (2房)
 $1232万
-$25,184/呎
+$25,236/呎
 (24年-03月-18日)</t>
         </is>
       </c>
@@ -56742,9 +56742,9 @@
       </c>
       <c r="B38" s="21" t="inlineStr">
         <is>
-          <t>A | 765呎 (3房)
+          <t>A | 766呎 (3房)
 $2402万
-$31,399/呎
+$31,358/呎
 (24年-04月-18日)</t>
         </is>
       </c>
@@ -56766,9 +56766,9 @@
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>D | 572呎 (2房)
+          <t>D | 571呎 (2房)
 $1703万
-$29,774/呎
+$29,827/呎
 (24年-01月-08日)</t>
         </is>
       </c>
@@ -56950,17 +56950,17 @@
       </c>
       <c r="C5" s="21" t="inlineStr">
         <is>
-          <t>B | 966呎 (4+房)
+          <t>B | 965呎 (4+房)
 $3351万
-$34,687/呎
+$34,723/呎
 (26年-03月-19日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t>C | 1067呎 (3房)
+          <t>C | 1057呎 (3房)
 $4700万
-$44,049/呎
+$44,465/呎
 (26年-06月-05日)</t>
         </is>
       </c>
@@ -56975,9 +56975,9 @@
       </c>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t>A | 1301呎 (4+房)
+          <t>A | 1302呎 (4+房)
 $4363万
-$33,539/呎
+$33,513/呎
 (26年-01月-28日)</t>
         </is>
       </c>
@@ -57008,17 +57008,17 @@
       </c>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t>A | 1301呎 (4+房)
+          <t>A | 1302呎 (4+房)
 $4340万
-$33,359/呎
+$33,333/呎
 (25年-07月-03日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
         <is>
-          <t>B | 966呎 (4+房)
+          <t>B | 965呎 (4+房)
 $3275万
-$33,900/呎
+$33,935/呎
 (26年-03月-31日)</t>
         </is>
       </c>
@@ -57041,17 +57041,17 @@
       </c>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t>A | 1301呎 (4+房)
+          <t>A | 1302呎 (4+房)
 $4470万
-$34,359/呎
+$34,332/呎
 (24年-04月-09日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>B | 966呎 (4+房)
+          <t>B | 965呎 (4+房)
 $3242万
-$33,563/呎
+$33,598/呎
 (26年-04月-09日)</t>
         </is>
       </c>
